--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany 3. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany 3. Liga_20242025.xlsx
@@ -21439,10 +21439,10 @@
         <v>7</v>
       </c>
       <c r="BB96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD96" t="n">
         <v>0</v>
@@ -36699,10 +36699,10 @@
         <v>6</v>
       </c>
       <c r="BB166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC166" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD166" t="n">
         <v>2.38</v>
@@ -38443,10 +38443,10 @@
         <v>5</v>
       </c>
       <c r="BB174" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC174" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD174" t="n">
         <v>1.69</v>
